--- a/data/kindergarten/data(4).xlsx
+++ b/data/kindergarten/data(4).xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,7 +806,7 @@
         <v>高松市牟礼町牟礼1243-2</v>
       </c>
       <c r="F16" t="str">
-        <v>087-845-3701</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/youchien_hoiku/kodomoen/chiiki_suishin/gaiyou.html</v>
@@ -826,13 +826,13 @@
         <v>134.148384</v>
       </c>
       <c r="D17" t="str">
-        <v>高松市立大町幼稚園</v>
+        <v>旧高松市立大町幼稚園</v>
       </c>
       <c r="E17" t="str">
         <v>高松市牟礼町牟礼100-1</v>
       </c>
       <c r="F17" t="str">
-        <v>087-845-5718</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/youchien_hoiku/kodomoen/chiiki_suishin/gaiyou.html</v>
@@ -2167,9 +2167,257 @@
         <v>私立認定こども園</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>75</v>
+      </c>
+      <c r="B69" t="str">
+        <v>34.276948979637865</v>
+      </c>
+      <c r="C69" t="str">
+        <v>134.09146217391202</v>
+      </c>
+      <c r="D69" t="str">
+        <v>川島こども園</v>
+      </c>
+      <c r="E69" t="str">
+        <v>高松市川島東町２５３−４ 高松市立川島保育所</v>
+      </c>
+      <c r="F69" t="str">
+        <v>087-848-1978</v>
+      </c>
+      <c r="H69" t="str">
+        <v>市立認定こども園</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>76</v>
+      </c>
+      <c r="B70" t="str">
+        <v>34.257703446058855</v>
+      </c>
+      <c r="C70" t="str">
+        <v>134.0369180917345</v>
+      </c>
+      <c r="D70" t="str">
+        <v>浅野こども園</v>
+      </c>
+      <c r="E70" t="str">
+        <v>高松市香川町浅野８１６−１</v>
+      </c>
+      <c r="F70" t="str">
+        <v>087-889-2416</v>
+      </c>
+      <c r="H70" t="str">
+        <v>市立認定こども園</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>77</v>
+      </c>
+      <c r="B71" t="str">
+        <v xml:space="preserve"> 34.30041785647681</v>
+      </c>
+      <c r="C71" t="str">
+        <v>134.11587552410276</v>
+      </c>
+      <c r="D71" t="str">
+        <v>認定こども園西光寺保育所</v>
+      </c>
+      <c r="E71" t="str">
+        <v>高松市前田西町１６７−１</v>
+      </c>
+      <c r="F71" t="str">
+        <v>087-847-6237</v>
+      </c>
+      <c r="H71" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>78</v>
+      </c>
+      <c r="B72" t="str">
+        <v>34.29993596569205</v>
+      </c>
+      <c r="C72" t="str">
+        <v>134.09232775107418</v>
+      </c>
+      <c r="D72" t="str">
+        <v>幼保連携型認定こども園川添こども園</v>
+      </c>
+      <c r="E72" t="str">
+        <v>高松市下田井町５２</v>
+      </c>
+      <c r="F72" t="str">
+        <v>087-847-5078</v>
+      </c>
+      <c r="G72" t="str">
+        <v>http://kawazoe-hoikuen.jp/publics/index/13/</v>
+      </c>
+      <c r="H72" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>79</v>
+      </c>
+      <c r="B73" t="str">
+        <v>34.284998062405684</v>
+      </c>
+      <c r="C73" t="str">
+        <v>134.00990618342553</v>
+      </c>
+      <c r="D73" t="str">
+        <v>幼保連携型円座百華こども園</v>
+      </c>
+      <c r="E73" t="str">
+        <v>高松市円座町１４７８−１</v>
+      </c>
+      <c r="F73" t="str">
+        <v>087-885-0907</v>
+      </c>
+      <c r="H73" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>80</v>
+      </c>
+      <c r="B74" t="str">
+        <v>34.33324182203997</v>
+      </c>
+      <c r="C74" t="str">
+        <v>134.05551890726952</v>
+      </c>
+      <c r="D74" t="str">
+        <v>認定こども園高松くりの木学舎</v>
+      </c>
+      <c r="E74" t="str">
+        <v>高松市花園町３丁目４−５</v>
+      </c>
+      <c r="F74" t="str">
+        <v>087-880-7211</v>
+      </c>
+      <c r="G74" t="str">
+        <v>https://nagaofukushikai.jp/business/t-kurinoki/</v>
+      </c>
+      <c r="H74" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>81</v>
+      </c>
+      <c r="B75" t="str">
+        <v xml:space="preserve"> 34.30482883155298</v>
+      </c>
+      <c r="C75" t="str">
+        <v>134.02164980843062</v>
+      </c>
+      <c r="D75" t="str">
+        <v>幼保連携型勅使百華こども園</v>
+      </c>
+      <c r="E75" t="str">
+        <v>高松市勅使町９５５</v>
+      </c>
+      <c r="F75" t="str">
+        <v>087-865-2998</v>
+      </c>
+      <c r="G75" t="str">
+        <v>https://www.chokushi-hyakka.or.jp/</v>
+      </c>
+      <c r="H75" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>82</v>
+      </c>
+      <c r="B76" t="str">
+        <v>34.25734690976807</v>
+      </c>
+      <c r="C76" t="str">
+        <v>134.0356786848988</v>
+      </c>
+      <c r="D76" t="str">
+        <v>さんさんこども園</v>
+      </c>
+      <c r="E76" t="str">
+        <v>高松市香川町浅野８３４−１</v>
+      </c>
+      <c r="F76" t="str">
+        <v>087-888-6333</v>
+      </c>
+      <c r="G76" t="str">
+        <v>http://www.sansan-kai.com/</v>
+      </c>
+      <c r="H76" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>83</v>
+      </c>
+      <c r="B77" t="str">
+        <v>34.29195613890213</v>
+      </c>
+      <c r="C77" t="str">
+        <v>134.07534629066907</v>
+      </c>
+      <c r="D77" t="str">
+        <v>幼保連携型認定こども園あさがおこども園</v>
+      </c>
+      <c r="E77" t="str">
+        <v>高松市上林町６９</v>
+      </c>
+      <c r="F77" t="str">
+        <v>087-899-5660</v>
+      </c>
+      <c r="G77" t="str">
+        <v>https://syurikai.com/facility/asagao/</v>
+      </c>
+      <c r="H77" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>84</v>
+      </c>
+      <c r="B78" t="str">
+        <v>34.29195613890213</v>
+      </c>
+      <c r="C78" t="str">
+        <v>134.07534629066907</v>
+      </c>
+      <c r="D78" t="str">
+        <v>にこにここども園</v>
+      </c>
+      <c r="E78" t="str">
+        <v>高松市林町３５１−３０</v>
+      </c>
+      <c r="F78" t="str">
+        <v>087-813-8300</v>
+      </c>
+      <c r="G78" t="str">
+        <v>https://nikoniko-fukushi.com/niconico/niconico/</v>
+      </c>
+      <c r="H78" t="str">
+        <v>私立認定こども園</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H78"/>
   </ignoredErrors>
 </worksheet>
 </file>